--- a/ListsForDB/Doctor_Clean.xlsx
+++ b/ListsForDB/Doctor_Clean.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="54">
   <si>
     <t>amka</t>
   </si>
@@ -59,6 +59,123 @@
   </si>
   <si>
     <t>RESIDENT</t>
+  </si>
+  <si>
+    <t>\N</t>
+  </si>
+  <si>
+    <t>75339133780</t>
+  </si>
+  <si>
+    <t>21389790404</t>
+  </si>
+  <si>
+    <t>95448079151</t>
+  </si>
+  <si>
+    <t>33860842912</t>
+  </si>
+  <si>
+    <t>53434182353</t>
+  </si>
+  <si>
+    <t>32379434579</t>
+  </si>
+  <si>
+    <t>56784597458</t>
+  </si>
+  <si>
+    <t>36702445480</t>
+  </si>
+  <si>
+    <t>81344410739</t>
+  </si>
+  <si>
+    <t>19276620746</t>
+  </si>
+  <si>
+    <t>89981892222</t>
+  </si>
+  <si>
+    <t>80036372124</t>
+  </si>
+  <si>
+    <t>62066779638</t>
+  </si>
+  <si>
+    <t>18193427864</t>
+  </si>
+  <si>
+    <t>60552999461</t>
+  </si>
+  <si>
+    <t>35895166626</t>
+  </si>
+  <si>
+    <t>60344799227</t>
+  </si>
+  <si>
+    <t>96575194408</t>
+  </si>
+  <si>
+    <t>90656248238</t>
+  </si>
+  <si>
+    <t>91367023329</t>
+  </si>
+  <si>
+    <t>52288372388</t>
+  </si>
+  <si>
+    <t>60334753081</t>
+  </si>
+  <si>
+    <t>13706183648</t>
+  </si>
+  <si>
+    <t>31551628292</t>
+  </si>
+  <si>
+    <t>30639295654</t>
+  </si>
+  <si>
+    <t>98451520706</t>
+  </si>
+  <si>
+    <t>37233268274</t>
+  </si>
+  <si>
+    <t>31976884284</t>
+  </si>
+  <si>
+    <t>67697807470</t>
+  </si>
+  <si>
+    <t>35134846364</t>
+  </si>
+  <si>
+    <t>45979296668</t>
+  </si>
+  <si>
+    <t>38538288127</t>
+  </si>
+  <si>
+    <t>47960718664</t>
+  </si>
+  <si>
+    <t>92698522280</t>
+  </si>
+  <si>
+    <t>83923788555</t>
+  </si>
+  <si>
+    <t>51927673524</t>
+  </si>
+  <si>
+    <t>77117947422</t>
+  </si>
+  <si>
+    <t>20287442157</t>
   </si>
 </sst>
 </file>
@@ -449,6 +566,9 @@
       <c r="D2" t="s">
         <v>11</v>
       </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
@@ -463,8 +583,8 @@
       <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="E3">
-        <v>813444107390</v>
+      <c r="E3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -480,8 +600,8 @@
       <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="E4">
-        <v>839237885550</v>
+      <c r="E4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -497,6 +617,9 @@
       <c r="D5" t="s">
         <v>11</v>
       </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
@@ -511,8 +634,8 @@
       <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="E6">
-        <v>946134267760</v>
+      <c r="E6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -528,8 +651,8 @@
       <c r="D7" t="s">
         <v>14</v>
       </c>
-      <c r="E7">
-        <v>315516282920</v>
+      <c r="E7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -545,8 +668,8 @@
       <c r="D8" t="s">
         <v>13</v>
       </c>
-      <c r="E8">
-        <v>946134267760</v>
+      <c r="E8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -562,8 +685,8 @@
       <c r="D9" t="s">
         <v>14</v>
       </c>
-      <c r="E9">
-        <v>225612834520</v>
+      <c r="E9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -579,8 +702,8 @@
       <c r="D10" t="s">
         <v>12</v>
       </c>
-      <c r="E10">
-        <v>748953262920</v>
+      <c r="E10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -596,8 +719,8 @@
       <c r="D11" t="s">
         <v>13</v>
       </c>
-      <c r="E11">
-        <v>192766207460</v>
+      <c r="E11" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -613,8 +736,8 @@
       <c r="D12" t="s">
         <v>13</v>
       </c>
-      <c r="E12">
-        <v>603447992270</v>
+      <c r="E12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -630,8 +753,8 @@
       <c r="D13" t="s">
         <v>13</v>
       </c>
-      <c r="E13">
-        <v>408896894020</v>
+      <c r="E13" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -647,8 +770,8 @@
       <c r="D14" t="s">
         <v>13</v>
       </c>
-      <c r="E14">
-        <v>408896894020</v>
+      <c r="E14" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -664,8 +787,8 @@
       <c r="D15" t="s">
         <v>14</v>
       </c>
-      <c r="E15">
-        <v>771179474220</v>
+      <c r="E15" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -681,8 +804,8 @@
       <c r="D16" t="s">
         <v>12</v>
       </c>
-      <c r="E16">
-        <v>367024454800</v>
+      <c r="E16" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -698,8 +821,8 @@
       <c r="D17" t="s">
         <v>13</v>
       </c>
-      <c r="E17">
-        <v>926985222800</v>
+      <c r="E17" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -715,8 +838,8 @@
       <c r="D18" t="s">
         <v>12</v>
       </c>
-      <c r="E18">
-        <v>771179474220</v>
+      <c r="E18" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -732,6 +855,9 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
@@ -746,8 +872,8 @@
       <c r="D20" t="s">
         <v>12</v>
       </c>
-      <c r="E20">
-        <v>926985222800</v>
+      <c r="E20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -763,8 +889,8 @@
       <c r="D21" t="s">
         <v>14</v>
       </c>
-      <c r="E21">
-        <v>392435624390</v>
+      <c r="E21" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -780,8 +906,8 @@
       <c r="D22" t="s">
         <v>14</v>
       </c>
-      <c r="E22">
-        <v>351348463640</v>
+      <c r="E22" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -797,8 +923,8 @@
       <c r="D23" t="s">
         <v>12</v>
       </c>
-      <c r="E23">
-        <v>367024454800</v>
+      <c r="E23" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -814,8 +940,8 @@
       <c r="D24" t="s">
         <v>14</v>
       </c>
-      <c r="E24">
-        <v>901345087780</v>
+      <c r="E24" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -831,8 +957,8 @@
       <c r="D25" t="s">
         <v>12</v>
       </c>
-      <c r="E25">
-        <v>319768842840</v>
+      <c r="E25" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -848,8 +974,8 @@
       <c r="D26" t="s">
         <v>13</v>
       </c>
-      <c r="E26">
-        <v>839237885550</v>
+      <c r="E26" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -865,8 +991,8 @@
       <c r="D27" t="s">
         <v>13</v>
       </c>
-      <c r="E27">
-        <v>946134267760</v>
+      <c r="E27" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -882,8 +1008,8 @@
       <c r="D28" t="s">
         <v>14</v>
       </c>
-      <c r="E28">
-        <v>813444107390</v>
+      <c r="E28" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -899,6 +1025,9 @@
       <c r="D29" t="s">
         <v>11</v>
       </c>
+      <c r="E29" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
@@ -913,6 +1042,9 @@
       <c r="D30" t="s">
         <v>11</v>
       </c>
+      <c r="E30" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
@@ -927,8 +1059,8 @@
       <c r="D31" t="s">
         <v>12</v>
       </c>
-      <c r="E31">
-        <v>753391337800</v>
+      <c r="E31" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -944,8 +1076,8 @@
       <c r="D32" t="s">
         <v>13</v>
       </c>
-      <c r="E32">
-        <v>367024454800</v>
+      <c r="E32" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -961,8 +1093,8 @@
       <c r="D33" t="s">
         <v>14</v>
       </c>
-      <c r="E33">
-        <v>192766207460</v>
+      <c r="E33" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -978,6 +1110,9 @@
       <c r="D34" t="s">
         <v>11</v>
       </c>
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
@@ -992,8 +1127,8 @@
       <c r="D35" t="s">
         <v>12</v>
       </c>
-      <c r="E35">
-        <v>753391337800</v>
+      <c r="E35" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1009,8 +1144,8 @@
       <c r="D36" t="s">
         <v>12</v>
       </c>
-      <c r="E36">
-        <v>603347530810</v>
+      <c r="E36" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1026,8 +1161,8 @@
       <c r="D37" t="s">
         <v>12</v>
       </c>
-      <c r="E37">
-        <v>567845974580</v>
+      <c r="E37" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1043,6 +1178,9 @@
       <c r="D38" t="s">
         <v>11</v>
       </c>
+      <c r="E38" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
@@ -1057,8 +1195,8 @@
       <c r="D39" t="s">
         <v>14</v>
       </c>
-      <c r="E39">
-        <v>367024454800</v>
+      <c r="E39" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1074,8 +1212,8 @@
       <c r="D40" t="s">
         <v>12</v>
       </c>
-      <c r="E40">
-        <v>479607186640</v>
+      <c r="E40" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1091,6 +1229,9 @@
       <c r="D41" t="s">
         <v>11</v>
       </c>
+      <c r="E41" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
@@ -1105,8 +1246,8 @@
       <c r="D42" t="s">
         <v>14</v>
       </c>
-      <c r="E42">
-        <v>901345087780</v>
+      <c r="E42" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1122,8 +1263,8 @@
       <c r="D43" t="s">
         <v>12</v>
       </c>
-      <c r="E43">
-        <v>567845974580</v>
+      <c r="E43" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1139,8 +1280,8 @@
       <c r="D44" t="s">
         <v>13</v>
       </c>
-      <c r="E44">
-        <v>408896894020</v>
+      <c r="E44" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1156,8 +1297,8 @@
       <c r="D45" t="s">
         <v>13</v>
       </c>
-      <c r="E45">
-        <v>213897904040</v>
+      <c r="E45" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1173,8 +1314,8 @@
       <c r="D46" t="s">
         <v>13</v>
       </c>
-      <c r="E46">
-        <v>972872106910</v>
+      <c r="E46" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1190,8 +1331,8 @@
       <c r="D47" t="s">
         <v>14</v>
       </c>
-      <c r="E47">
-        <v>519276735240</v>
+      <c r="E47" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1207,8 +1348,8 @@
       <c r="D48" t="s">
         <v>12</v>
       </c>
-      <c r="E48">
-        <v>367024454800</v>
+      <c r="E48" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1224,8 +1365,8 @@
       <c r="D49" t="s">
         <v>12</v>
       </c>
-      <c r="E49">
-        <v>137061836480</v>
+      <c r="E49" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1241,8 +1382,8 @@
       <c r="D50" t="s">
         <v>14</v>
       </c>
-      <c r="E50">
-        <v>965751944080</v>
+      <c r="E50" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1258,8 +1399,8 @@
       <c r="D51" t="s">
         <v>14</v>
       </c>
-      <c r="E51">
-        <v>800363721240</v>
+      <c r="E51" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1275,8 +1416,8 @@
       <c r="D52" t="s">
         <v>13</v>
       </c>
-      <c r="E52">
-        <v>319768842840</v>
+      <c r="E52" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1292,8 +1433,8 @@
       <c r="D53" t="s">
         <v>14</v>
       </c>
-      <c r="E53">
-        <v>839237885550</v>
+      <c r="E53" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1309,8 +1450,8 @@
       <c r="D54" t="s">
         <v>14</v>
       </c>
-      <c r="E54">
-        <v>213897904040</v>
+      <c r="E54" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1326,8 +1467,8 @@
       <c r="D55" t="s">
         <v>12</v>
       </c>
-      <c r="E55">
-        <v>484868751220</v>
+      <c r="E55" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1343,8 +1484,8 @@
       <c r="D56" t="s">
         <v>14</v>
       </c>
-      <c r="E56">
-        <v>913670233290</v>
+      <c r="E56" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1360,8 +1501,8 @@
       <c r="D57" t="s">
         <v>14</v>
       </c>
-      <c r="E57">
-        <v>225854134840</v>
+      <c r="E57" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1377,8 +1518,8 @@
       <c r="D58" t="s">
         <v>12</v>
       </c>
-      <c r="E58">
-        <v>202874421570</v>
+      <c r="E58" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1394,8 +1535,8 @@
       <c r="D59" t="s">
         <v>12</v>
       </c>
-      <c r="E59">
-        <v>620667796380</v>
+      <c r="E59" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1411,8 +1552,8 @@
       <c r="D60" t="s">
         <v>13</v>
       </c>
-      <c r="E60">
-        <v>603447992270</v>
+      <c r="E60" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1428,6 +1569,9 @@
       <c r="D61" t="s">
         <v>11</v>
       </c>
+      <c r="E61" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
@@ -1442,8 +1586,8 @@
       <c r="D62" t="s">
         <v>12</v>
       </c>
-      <c r="E62">
-        <v>181934278640</v>
+      <c r="E62" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1459,6 +1603,9 @@
       <c r="D63" t="s">
         <v>11</v>
       </c>
+      <c r="E63" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
@@ -1473,8 +1620,8 @@
       <c r="D64" t="s">
         <v>13</v>
       </c>
-      <c r="E64">
-        <v>408896894020</v>
+      <c r="E64" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1490,6 +1637,9 @@
       <c r="D65" t="s">
         <v>11</v>
       </c>
+      <c r="E65" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
@@ -1504,8 +1654,8 @@
       <c r="D66" t="s">
         <v>13</v>
       </c>
-      <c r="E66">
-        <v>926985222800</v>
+      <c r="E66" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1521,8 +1671,8 @@
       <c r="D67" t="s">
         <v>13</v>
       </c>
-      <c r="E67">
-        <v>813444107390</v>
+      <c r="E67" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1538,8 +1688,8 @@
       <c r="D68" t="s">
         <v>12</v>
       </c>
-      <c r="E68">
-        <v>603447992270</v>
+      <c r="E68" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1555,6 +1705,9 @@
       <c r="D69" t="s">
         <v>11</v>
       </c>
+      <c r="E69" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
@@ -1569,6 +1722,9 @@
       <c r="D70" t="s">
         <v>11</v>
       </c>
+      <c r="E70" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
@@ -1583,8 +1739,8 @@
       <c r="D71" t="s">
         <v>12</v>
       </c>
-      <c r="E71">
-        <v>620667796380</v>
+      <c r="E71" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1600,6 +1756,9 @@
       <c r="D72" t="s">
         <v>11</v>
       </c>
+      <c r="E72" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
@@ -1614,8 +1773,8 @@
       <c r="D73" t="s">
         <v>14</v>
       </c>
-      <c r="E73">
-        <v>338608429120</v>
+      <c r="E73" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1631,8 +1790,8 @@
       <c r="D74" t="s">
         <v>14</v>
       </c>
-      <c r="E74">
-        <v>800363721240</v>
+      <c r="E74" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1648,8 +1807,8 @@
       <c r="D75" t="s">
         <v>12</v>
       </c>
-      <c r="E75">
-        <v>306392956540</v>
+      <c r="E75" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1665,6 +1824,9 @@
       <c r="D76" t="s">
         <v>11</v>
       </c>
+      <c r="E76" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
@@ -1679,8 +1841,8 @@
       <c r="D77" t="s">
         <v>12</v>
       </c>
-      <c r="E77">
-        <v>479607186640</v>
+      <c r="E77" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1696,8 +1858,8 @@
       <c r="D78" t="s">
         <v>12</v>
       </c>
-      <c r="E78">
-        <v>306392956540</v>
+      <c r="E78" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1713,8 +1875,8 @@
       <c r="D79" t="s">
         <v>12</v>
       </c>
-      <c r="E79">
-        <v>338608429120</v>
+      <c r="E79" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1730,8 +1892,8 @@
       <c r="D80" t="s">
         <v>14</v>
       </c>
-      <c r="E80">
-        <v>319768842840</v>
+      <c r="E80" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1747,8 +1909,8 @@
       <c r="D81" t="s">
         <v>13</v>
       </c>
-      <c r="E81">
-        <v>972872106910</v>
+      <c r="E81" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
